--- a/nseIndia/exportedData/LiveAnalysisVariationsGainersData.xlsx
+++ b/nseIndia/exportedData/LiveAnalysisVariationsGainersData.xlsx
@@ -506,7 +506,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>WIPRO</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -515,28 +515,28 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>243.1</v>
+        <v>402</v>
       </c>
       <c r="D2" t="n">
-        <v>248.43</v>
+        <v>410.45</v>
       </c>
       <c r="E2" t="n">
-        <v>242.41</v>
+        <v>401.9</v>
       </c>
       <c r="F2" t="n">
-        <v>247.1</v>
+        <v>409.5</v>
       </c>
       <c r="G2" t="n">
-        <v>241.65</v>
+        <v>400.9</v>
       </c>
       <c r="H2" t="n">
-        <v>2.26</v>
+        <v>2.15</v>
       </c>
       <c r="I2" t="n">
-        <v>6604129</v>
+        <v>25255050</v>
       </c>
       <c r="J2" t="n">
-        <v>16255.4031206</v>
+        <v>102924.43077</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -545,22 +545,22 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>28-Jul-2025</t>
+          <t>28-May-2025</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Interim Dividend - Rs 5 Per Share</t>
+          <t>Dividend - Rs 7.85 Per Share</t>
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.26</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>INFY</t>
+          <t>SHRIRAMFIN</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -569,28 +569,28 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1426.2</v>
+        <v>570.5</v>
       </c>
       <c r="D3" t="n">
-        <v>1470</v>
+        <v>588.65</v>
       </c>
       <c r="E3" t="n">
-        <v>1426.2</v>
+        <v>566.5</v>
       </c>
       <c r="F3" t="n">
-        <v>1455.4</v>
+        <v>581.9</v>
       </c>
       <c r="G3" t="n">
-        <v>1426.6</v>
+        <v>571.65</v>
       </c>
       <c r="H3" t="n">
-        <v>2.02</v>
+        <v>1.79</v>
       </c>
       <c r="I3" t="n">
-        <v>7582525</v>
+        <v>12979613</v>
       </c>
       <c r="J3" t="n">
-        <v>110182.4290275</v>
+        <v>71144.685432</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -599,22 +599,22 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>30-May-2025</t>
+          <t>11-Jul-2025</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Dividend - Rs 22 Per Share</t>
+          <t>Dividend - Rs 3 Per Share</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.02</v>
+        <v>1.79</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>HDFCLIFE</t>
+          <t>BEL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -623,28 +623,28 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>778.75</v>
+        <v>362.3</v>
       </c>
       <c r="D4" t="n">
-        <v>790.75</v>
+        <v>371</v>
       </c>
       <c r="E4" t="n">
-        <v>777.95</v>
+        <v>361.6</v>
       </c>
       <c r="F4" t="n">
-        <v>787.05</v>
+        <v>369.4</v>
       </c>
       <c r="G4" t="n">
-        <v>776.6</v>
+        <v>363.85</v>
       </c>
       <c r="H4" t="n">
-        <v>1.35</v>
+        <v>1.53</v>
       </c>
       <c r="I4" t="n">
-        <v>1551742</v>
+        <v>12739664</v>
       </c>
       <c r="J4" t="n">
-        <v>12215.313024</v>
+        <v>46938.0180416</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -653,22 +653,22 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>20-Jun-2025</t>
+          <t>14-Aug-2025</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Dividend - Rs 2.10 Per Share</t>
+          <t>Dividend - Rs 0.90 Per Share</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.35</v>
+        <v>1.53</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -677,28 +677,28 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>313</v>
+        <v>3575.6</v>
       </c>
       <c r="D5" t="n">
-        <v>316.55</v>
+        <v>3615</v>
       </c>
       <c r="E5" t="n">
-        <v>310.65</v>
+        <v>3540.2</v>
       </c>
       <c r="F5" t="n">
-        <v>316</v>
+        <v>3605</v>
       </c>
       <c r="G5" t="n">
-        <v>312.35</v>
+        <v>3560.1</v>
       </c>
       <c r="H5" t="n">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="I5" t="n">
-        <v>17571060</v>
+        <v>1678055</v>
       </c>
       <c r="J5" t="n">
-        <v>55069.459146</v>
+        <v>60304.262535</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -707,22 +707,22 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>03-Jun-2025</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Dividend - Rs 34 Per Share</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BHARTIARTL</t>
+          <t>ASIANPAINT</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -731,28 +731,28 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1873</v>
+        <v>2491</v>
       </c>
       <c r="D6" t="n">
-        <v>1883</v>
+        <v>2531.6</v>
       </c>
       <c r="E6" t="n">
-        <v>1866.8</v>
+        <v>2490</v>
       </c>
       <c r="F6" t="n">
-        <v>1879.8</v>
+        <v>2520</v>
       </c>
       <c r="G6" t="n">
-        <v>1867.4</v>
+        <v>2489</v>
       </c>
       <c r="H6" t="n">
-        <v>0.66</v>
+        <v>1.25</v>
       </c>
       <c r="I6" t="n">
-        <v>2193903</v>
+        <v>1798653</v>
       </c>
       <c r="J6" t="n">
-        <v>41167.0540629</v>
+        <v>45203.9270613</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -761,22 +761,22 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>18-Jul-2025</t>
+          <t>10-Jun-2025</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Dividend - Rs 16 Per Share</t>
+          <t>Dividend - Rs 20.55 Per Share</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0.66</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>HDFCBANK</t>
+          <t>TRENT</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -785,28 +785,28 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1978</v>
+        <v>5239</v>
       </c>
       <c r="D7" t="n">
-        <v>1994.8</v>
+        <v>5411</v>
       </c>
       <c r="E7" t="n">
-        <v>1971.2</v>
+        <v>5230</v>
       </c>
       <c r="F7" t="n">
-        <v>1991.9</v>
+        <v>5292</v>
       </c>
       <c r="G7" t="n">
-        <v>1980.3</v>
+        <v>5235.5</v>
       </c>
       <c r="H7" t="n">
-        <v>0.59</v>
+        <v>1.08</v>
       </c>
       <c r="I7" t="n">
-        <v>3639844</v>
+        <v>1333724</v>
       </c>
       <c r="J7" t="n">
-        <v>72349.90715680001</v>
+        <v>71153.77528279999</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -815,22 +815,22 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>26-Aug-2025</t>
+          <t>12-Jun-2025</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Bonus 1:1</t>
+          <t>Dividend - Rs 5 Per Share</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0.59</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BAJAJFINSV</t>
+          <t>ULTRACEMCO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -839,28 +839,28 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1914.4</v>
+        <v>12521</v>
       </c>
       <c r="D8" t="n">
-        <v>1939.1</v>
+        <v>12729</v>
       </c>
       <c r="E8" t="n">
-        <v>1912.5</v>
+        <v>12521</v>
       </c>
       <c r="F8" t="n">
-        <v>1925.5</v>
+        <v>12635</v>
       </c>
       <c r="G8" t="n">
-        <v>1914.4</v>
+        <v>12521</v>
       </c>
       <c r="H8" t="n">
-        <v>0.58</v>
+        <v>0.91</v>
       </c>
       <c r="I8" t="n">
-        <v>389118</v>
+        <v>177858</v>
       </c>
       <c r="J8" t="n">
-        <v>7501.3000686</v>
+        <v>22508.1433296</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -869,22 +869,22 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>27-Jun-2025</t>
+          <t>25-Jul-2025</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Dividend - Re 1 Per Share</t>
+          <t>Dividend - Rs 77.50 Per Sh</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0.58</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SBIN</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -893,28 +893,28 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>822</v>
+        <v>1950.2</v>
       </c>
       <c r="D9" t="n">
-        <v>828</v>
+        <v>1984.9</v>
       </c>
       <c r="E9" t="n">
-        <v>819.1</v>
+        <v>1950.2</v>
       </c>
       <c r="F9" t="n">
-        <v>826.35</v>
+        <v>1959.2</v>
       </c>
       <c r="G9" t="n">
-        <v>821.85</v>
+        <v>1944.7</v>
       </c>
       <c r="H9" t="n">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="I9" t="n">
-        <v>3298787</v>
+        <v>3250051</v>
       </c>
       <c r="J9" t="n">
-        <v>27228.187898</v>
+        <v>60456.6351984</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -923,22 +923,22 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>16-May-2025</t>
+          <t>18-Jul-2025</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Dividend - Rs 15.90 Per Share</t>
+          <t>Dividend - Rs 2.50 Per Share</t>
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>DRREDDY</t>
+          <t>SUNPHARMA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -947,28 +947,28 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1255.1</v>
+        <v>1581</v>
       </c>
       <c r="D10" t="n">
-        <v>1266</v>
+        <v>1601.7</v>
       </c>
       <c r="E10" t="n">
-        <v>1251</v>
+        <v>1575.8</v>
       </c>
       <c r="F10" t="n">
-        <v>1260.2</v>
+        <v>1595.7</v>
       </c>
       <c r="G10" t="n">
-        <v>1253.4</v>
+        <v>1585.7</v>
       </c>
       <c r="H10" t="n">
-        <v>0.54</v>
+        <v>0.63</v>
       </c>
       <c r="I10" t="n">
-        <v>408451</v>
+        <v>3176534</v>
       </c>
       <c r="J10" t="n">
-        <v>5142.6431606</v>
+        <v>50577.0920014</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -977,22 +977,22 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>10-Jul-2025</t>
+          <t>07-Jul-2025</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Dividend - Rs 8 Per Share</t>
+          <t>Dividend - Rs 5.50 Per Share</t>
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0.54</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ADANIENT</t>
+          <t>TATASTEEL</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1001,28 +1001,28 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2288</v>
+        <v>154.5</v>
       </c>
       <c r="D11" t="n">
-        <v>2304</v>
+        <v>155.1</v>
       </c>
       <c r="E11" t="n">
-        <v>2267.7</v>
+        <v>153.05</v>
       </c>
       <c r="F11" t="n">
-        <v>2290.9</v>
+        <v>154.5</v>
       </c>
       <c r="G11" t="n">
-        <v>2280.1</v>
+        <v>153.63</v>
       </c>
       <c r="H11" t="n">
-        <v>0.47</v>
+        <v>0.57</v>
       </c>
       <c r="I11" t="n">
-        <v>552637</v>
+        <v>16971859</v>
       </c>
       <c r="J11" t="n">
-        <v>12632.1212823</v>
+        <v>26202.8531101</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1031,22 +1031,22 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>13-Jun-2025</t>
+          <t>06-Jun-2025</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Dividend - Rs 1.30 Per Share</t>
+          <t>Dividend - Rs 3.60 Per Share</t>
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0.47</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>EICHERMOT</t>
+          <t>POWERGRID</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1055,28 +1055,28 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>5710</v>
+        <v>273.6</v>
       </c>
       <c r="D12" t="n">
-        <v>5746.5</v>
+        <v>276.1</v>
       </c>
       <c r="E12" t="n">
-        <v>5710</v>
+        <v>272.25</v>
       </c>
       <c r="F12" t="n">
-        <v>5740</v>
+        <v>275.95</v>
       </c>
       <c r="G12" t="n">
-        <v>5714.5</v>
+        <v>274.45</v>
       </c>
       <c r="H12" t="n">
-        <v>0.45</v>
+        <v>0.55</v>
       </c>
       <c r="I12" t="n">
-        <v>110133</v>
+        <v>12841075</v>
       </c>
       <c r="J12" t="n">
-        <v>6314.1341427</v>
+        <v>35294.978745</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1085,22 +1085,22 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>01-Aug-2025</t>
+          <t>19-Aug-2025</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Dividend - Rs 70 Per Share</t>
+          <t>Dividend - Rs 1.25 Per Share</t>
         </is>
       </c>
       <c r="N12" t="n">
-        <v>0.45</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>HCLTECH</t>
+          <t>CIPLA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1109,28 +1109,28 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1501</v>
+        <v>1578.5</v>
       </c>
       <c r="D13" t="n">
-        <v>1516.2</v>
+        <v>1596.4</v>
       </c>
       <c r="E13" t="n">
-        <v>1495.7</v>
+        <v>1567.8</v>
       </c>
       <c r="F13" t="n">
-        <v>1507.8</v>
+        <v>1587</v>
       </c>
       <c r="G13" t="n">
-        <v>1501.1</v>
+        <v>1580.3</v>
       </c>
       <c r="H13" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="I13" t="n">
-        <v>1885172</v>
+        <v>1342344</v>
       </c>
       <c r="J13" t="n">
-        <v>28409.9190744</v>
+        <v>21300.7172952</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1139,22 +1139,22 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>18-Jul-2025</t>
+          <t>27-Jun-2025</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Interim Dividend - Rs 12 Per Share</t>
+          <t>Dividend - Rs 13 Per Share/Special Dividend - Rs 3 Per Share</t>
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>POWERGRID</t>
+          <t>JIOFIN</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1163,28 +1163,28 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>289.05</v>
+        <v>311</v>
       </c>
       <c r="D14" t="n">
-        <v>290.15</v>
+        <v>316.65</v>
       </c>
       <c r="E14" t="n">
-        <v>287.15</v>
+        <v>309.35</v>
       </c>
       <c r="F14" t="n">
-        <v>289.35</v>
+        <v>311.3</v>
       </c>
       <c r="G14" t="n">
-        <v>288.2</v>
+        <v>310.1</v>
       </c>
       <c r="H14" t="n">
-        <v>0.4</v>
+        <v>0.39</v>
       </c>
       <c r="I14" t="n">
-        <v>2506384</v>
+        <v>17274984</v>
       </c>
       <c r="J14" t="n">
-        <v>7242.6978448</v>
+        <v>54003.3274824</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1193,22 +1193,22 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>19-Aug-2025</t>
+          <t>11-Aug-2025</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Dividend - Rs 1.25 Per Share</t>
+          <t>Dividend - Re 0.50 Per Share</t>
         </is>
       </c>
       <c r="N14" t="n">
-        <v>0.4</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ICICIBANK</t>
+          <t>BHARTIARTL</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1217,28 +1217,28 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1412</v>
+        <v>1872.5</v>
       </c>
       <c r="D15" t="n">
-        <v>1430</v>
+        <v>1900.1</v>
       </c>
       <c r="E15" t="n">
-        <v>1412</v>
+        <v>1872.5</v>
       </c>
       <c r="F15" t="n">
-        <v>1426.2</v>
+        <v>1888.2</v>
       </c>
       <c r="G15" t="n">
-        <v>1420.8</v>
+        <v>1881.1</v>
       </c>
       <c r="H15" t="n">
         <v>0.38</v>
       </c>
       <c r="I15" t="n">
-        <v>2479017</v>
+        <v>4339042</v>
       </c>
       <c r="J15" t="n">
-        <v>35290.0465035</v>
+        <v>81892.909187</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1247,12 +1247,12 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>12-Aug-2025</t>
+          <t>18-Jul-2025</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Dividend - Rs 11 Per Share</t>
+          <t>Dividend - Rs 16 Per Share</t>
         </is>
       </c>
       <c r="N15" t="n">
@@ -1262,7 +1262,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>TITAN</t>
+          <t>HINDALCO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1271,28 +1271,28 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>3476.5</v>
+        <v>701</v>
       </c>
       <c r="D16" t="n">
-        <v>3488</v>
+        <v>708.75</v>
       </c>
       <c r="E16" t="n">
-        <v>3464.1</v>
+        <v>697</v>
       </c>
       <c r="F16" t="n">
-        <v>3479.9</v>
+        <v>704</v>
       </c>
       <c r="G16" t="n">
-        <v>3466.8</v>
+        <v>701.4</v>
       </c>
       <c r="H16" t="n">
-        <v>0.38</v>
+        <v>0.37</v>
       </c>
       <c r="I16" t="n">
-        <v>179462</v>
+        <v>5335149</v>
       </c>
       <c r="J16" t="n">
-        <v>6240.719265199999</v>
+        <v>37576.5214368</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1301,22 +1301,22 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>08-Jul-2025</t>
+          <t>08-Aug-2025</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Dividend - Rs 11 Per Share</t>
+          <t>Dividend - Rs 5 Per Share</t>
         </is>
       </c>
       <c r="N16" t="n">
-        <v>0.38</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ASIANPAINT</t>
+          <t>HEROMOTOCO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1325,28 +1325,28 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2505</v>
+        <v>5099.5</v>
       </c>
       <c r="D17" t="n">
-        <v>2514</v>
+        <v>5148.3</v>
       </c>
       <c r="E17" t="n">
-        <v>2497.7</v>
+        <v>5061.4</v>
       </c>
       <c r="F17" t="n">
-        <v>2506.9</v>
+        <v>5109.5</v>
       </c>
       <c r="G17" t="n">
-        <v>2500.2</v>
+        <v>5091.7</v>
       </c>
       <c r="H17" t="n">
-        <v>0.27</v>
+        <v>0.35</v>
       </c>
       <c r="I17" t="n">
-        <v>290323</v>
+        <v>783364</v>
       </c>
       <c r="J17" t="n">
-        <v>7273.8105066</v>
+        <v>39942.8686596</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -1355,22 +1355,22 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>10-Jun-2025</t>
+          <t>24-Jul-2025</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Dividend - Rs 20.55 Per Share</t>
+          <t>Dividend - Rs 65 Per Share</t>
         </is>
       </c>
       <c r="N17" t="n">
-        <v>0.27</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>HINDUNILVR</t>
+          <t>HCLTECH</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1379,28 +1379,28 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2498.9</v>
+        <v>1449.8</v>
       </c>
       <c r="D18" t="n">
-        <v>2509</v>
+        <v>1462.6</v>
       </c>
       <c r="E18" t="n">
-        <v>2492</v>
+        <v>1439.2</v>
       </c>
       <c r="F18" t="n">
-        <v>2501.7</v>
+        <v>1453.7</v>
       </c>
       <c r="G18" t="n">
-        <v>2495.1</v>
+        <v>1449.8</v>
       </c>
       <c r="H18" t="n">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="I18" t="n">
-        <v>297967</v>
+        <v>3404604</v>
       </c>
       <c r="J18" t="n">
-        <v>7450.486054800001</v>
+        <v>49565.2464132</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -1409,22 +1409,22 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>23-Jun-2025</t>
+          <t>18-Jul-2025</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Dividend - Rs 24 Per Share</t>
+          <t>Interim Dividend - Rs 12 Per Share</t>
         </is>
       </c>
       <c r="N18" t="n">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>BAJFINANCE</t>
+          <t>MARUTI</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1433,28 +1433,28 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>860</v>
+        <v>14750</v>
       </c>
       <c r="D19" t="n">
-        <v>866.9</v>
+        <v>14850</v>
       </c>
       <c r="E19" t="n">
-        <v>859.05</v>
+        <v>14692</v>
       </c>
       <c r="F19" t="n">
-        <v>861.75</v>
+        <v>14790</v>
       </c>
       <c r="G19" t="n">
-        <v>860</v>
+        <v>14752</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2</v>
+        <v>0.26</v>
       </c>
       <c r="I19" t="n">
-        <v>2057383</v>
+        <v>621560</v>
       </c>
       <c r="J19" t="n">
-        <v>17723.3258535</v>
+        <v>91826.415224</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -1463,22 +1463,22 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>16-Jun-2025</t>
+          <t>01-Aug-2025</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Bonus 4:1</t>
+          <t>Dividend - Rs 135 Per Share</t>
         </is>
       </c>
       <c r="N19" t="n">
-        <v>0.2</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CIPLA</t>
+          <t>BAJFINANCE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1487,28 +1487,28 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1562.5</v>
+        <v>870.85</v>
       </c>
       <c r="D20" t="n">
-        <v>1574.8</v>
+        <v>888</v>
       </c>
       <c r="E20" t="n">
-        <v>1552</v>
+        <v>870.85</v>
       </c>
       <c r="F20" t="n">
-        <v>1561.3</v>
+        <v>879</v>
       </c>
       <c r="G20" t="n">
-        <v>1561</v>
+        <v>876.85</v>
       </c>
       <c r="H20" t="n">
-        <v>0.02</v>
+        <v>0.25</v>
       </c>
       <c r="I20" t="n">
-        <v>849252</v>
+        <v>5672446</v>
       </c>
       <c r="J20" t="n">
-        <v>13273.2142836</v>
+        <v>49895.9695052</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -1517,22 +1517,22 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>27-Jun-2025</t>
+          <t>16-Jun-2025</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Dividend - Rs 13 Per Share/Special Dividend - Rs 3 Per Share</t>
+          <t>Bonus 4:1</t>
         </is>
       </c>
       <c r="N20" t="n">
-        <v>0.02</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>MARUTI</t>
+          <t>HINDUNILVR</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1541,28 +1541,28 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>12864</v>
+        <v>2664.8</v>
       </c>
       <c r="D21" t="n">
-        <v>12947</v>
+        <v>2723</v>
       </c>
       <c r="E21" t="n">
-        <v>12825</v>
+        <v>2641.4</v>
       </c>
       <c r="F21" t="n">
-        <v>12835</v>
+        <v>2660</v>
       </c>
       <c r="G21" t="n">
-        <v>12834</v>
+        <v>2654.4</v>
       </c>
       <c r="H21" t="n">
-        <v>0.01</v>
+        <v>0.21</v>
       </c>
       <c r="I21" t="n">
-        <v>99407</v>
+        <v>1972773</v>
       </c>
       <c r="J21" t="n">
-        <v>12805.3711632</v>
+        <v>52603.992045</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -1571,16 +1571,16 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>01-Aug-2025</t>
+          <t>23-Jun-2025</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Dividend - Rs 135 Per Share</t>
+          <t>Dividend - Rs 24 Per Share</t>
         </is>
       </c>
       <c r="N21" t="n">
-        <v>0.01</v>
+        <v>0.21</v>
       </c>
     </row>
   </sheetData>
@@ -1594,7 +1594,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N7"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1672,7 +1672,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AUBANK</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1681,28 +1681,28 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>744</v>
+        <v>1950.2</v>
       </c>
       <c r="D2" t="n">
-        <v>751.8</v>
+        <v>1984.9</v>
       </c>
       <c r="E2" t="n">
-        <v>740.55</v>
+        <v>1950.2</v>
       </c>
       <c r="F2" t="n">
-        <v>750.8</v>
+        <v>1959.2</v>
       </c>
       <c r="G2" t="n">
-        <v>738</v>
+        <v>1944.7</v>
       </c>
       <c r="H2" t="n">
-        <v>1.73</v>
+        <v>0.75</v>
       </c>
       <c r="I2" t="n">
-        <v>917891</v>
+        <v>3250051</v>
       </c>
       <c r="J2" t="n">
-        <v>6865.273945399999</v>
+        <v>60456.6351984</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -1711,22 +1711,22 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>04-Jul-2025</t>
+          <t>18-Jul-2025</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Dividend - Re 1 Per Share</t>
+          <t>Dividend - Rs 2.50 Per Share</t>
         </is>
       </c>
       <c r="N2" t="n">
-        <v>1.73</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>HDFCBANK</t>
+          <t>FEDERALBNK</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1735,28 +1735,28 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1978</v>
+        <v>191.3</v>
       </c>
       <c r="D3" t="n">
-        <v>1994.8</v>
+        <v>193.86</v>
       </c>
       <c r="E3" t="n">
-        <v>1971.2</v>
+        <v>191.12</v>
       </c>
       <c r="F3" t="n">
-        <v>1991.9</v>
+        <v>192.08</v>
       </c>
       <c r="G3" t="n">
-        <v>1980.3</v>
+        <v>191.76</v>
       </c>
       <c r="H3" t="n">
-        <v>0.59</v>
+        <v>0.17</v>
       </c>
       <c r="I3" t="n">
-        <v>3639844</v>
+        <v>4184028</v>
       </c>
       <c r="J3" t="n">
-        <v>72349.90715680001</v>
+        <v>8048.3962608</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -1765,16 +1765,16 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>26-Aug-2025</t>
+          <t>22-Aug-2025</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Bonus 1:1</t>
+          <t>Dividend - Rs 1.20 Per Share</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0.59</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="4">
@@ -1789,28 +1789,28 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>822</v>
+        <v>800.7</v>
       </c>
       <c r="D4" t="n">
-        <v>828</v>
+        <v>806.7</v>
       </c>
       <c r="E4" t="n">
-        <v>819.1</v>
+        <v>798.5</v>
       </c>
       <c r="F4" t="n">
-        <v>826.35</v>
+        <v>802.4</v>
       </c>
       <c r="G4" t="n">
-        <v>821.85</v>
+        <v>801.95</v>
       </c>
       <c r="H4" t="n">
-        <v>0.55</v>
+        <v>0.06</v>
       </c>
       <c r="I4" t="n">
-        <v>3298787</v>
+        <v>6861440</v>
       </c>
       <c r="J4" t="n">
-        <v>27228.187898</v>
+        <v>55096.677056</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -1828,13 +1828,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0.55</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ICICIBANK</t>
+          <t>IDFCFIRSTB</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1843,28 +1843,28 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1412</v>
+        <v>68</v>
       </c>
       <c r="D5" t="n">
-        <v>1430</v>
+        <v>69.3</v>
       </c>
       <c r="E5" t="n">
-        <v>1412</v>
+        <v>67.8</v>
       </c>
       <c r="F5" t="n">
-        <v>1426.2</v>
+        <v>68.08</v>
       </c>
       <c r="G5" t="n">
-        <v>1420.8</v>
+        <v>68.05</v>
       </c>
       <c r="H5" t="n">
-        <v>0.38</v>
+        <v>0.04</v>
       </c>
       <c r="I5" t="n">
-        <v>2479017</v>
+        <v>20587732</v>
       </c>
       <c r="J5" t="n">
-        <v>35290.0465035</v>
+        <v>14092.302554</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -1873,124 +1873,16 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>12-Aug-2025</t>
+          <t>11-Jul-2025</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Dividend - Rs 11 Per Share</t>
+          <t>Dividend - Rs 0.25 Per Share</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0.38</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>CANBK</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>EQ</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>109.5</v>
-      </c>
-      <c r="D6" t="n">
-        <v>109.88</v>
-      </c>
-      <c r="E6" t="n">
-        <v>108.63</v>
-      </c>
-      <c r="F6" t="n">
-        <v>109.3</v>
-      </c>
-      <c r="G6" t="n">
-        <v>108.99</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="I6" t="n">
-        <v>6237855</v>
-      </c>
-      <c r="J6" t="n">
-        <v>6814.8565875</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>13-Jun-2025</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>Dividend - Rs 4 Per Share</t>
-        </is>
-      </c>
-      <c r="N6" t="n">
-        <v>0.28</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>BANKBARODA</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>EQ</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>241.99</v>
-      </c>
-      <c r="D7" t="n">
-        <v>243.8</v>
-      </c>
-      <c r="E7" t="n">
-        <v>241.4</v>
-      </c>
-      <c r="F7" t="n">
-        <v>242.46</v>
-      </c>
-      <c r="G7" t="n">
-        <v>241.81</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="I7" t="n">
-        <v>2083270</v>
-      </c>
-      <c r="J7" t="n">
-        <v>5049.638153</v>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>06-Jun-2025</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>Dividend - Rs 8.35 Per Share</t>
-        </is>
-      </c>
-      <c r="N7" t="n">
-        <v>0.27</v>
+        <v>0.04</v>
       </c>
     </row>
   </sheetData>
@@ -2004,7 +1896,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N21"/>
+  <dimension ref="A1:N17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2082,7 +1974,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BAJAJHFL</t>
+          <t>CGPOWER</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2091,28 +1983,28 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>109.7</v>
+        <v>676.95</v>
       </c>
       <c r="D2" t="n">
-        <v>114.92</v>
+        <v>699.75</v>
       </c>
       <c r="E2" t="n">
-        <v>109.4</v>
+        <v>668.25</v>
       </c>
       <c r="F2" t="n">
-        <v>112.36</v>
+        <v>694</v>
       </c>
       <c r="G2" t="n">
-        <v>108.56</v>
+        <v>664</v>
       </c>
       <c r="H2" t="n">
-        <v>3.5</v>
+        <v>4.52</v>
       </c>
       <c r="I2" t="n">
-        <v>18805708</v>
+        <v>14580868</v>
       </c>
       <c r="J2" t="n">
-        <v>21291.8225976</v>
+        <v>100278.4615832</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -2121,22 +2013,22 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>21-Mar-2025</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Interim Dividend - Rs 1.30 Per Share</t>
         </is>
       </c>
       <c r="N2" t="n">
-        <v>3.5</v>
+        <v>4.52</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>NAUKRI</t>
+          <t>UNITDSPR</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -2145,28 +2037,28 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1329</v>
+        <v>1290</v>
       </c>
       <c r="D3" t="n">
-        <v>1374.5</v>
+        <v>1315.3</v>
       </c>
       <c r="E3" t="n">
-        <v>1319.5</v>
+        <v>1284.2</v>
       </c>
       <c r="F3" t="n">
-        <v>1362.1</v>
+        <v>1311</v>
       </c>
       <c r="G3" t="n">
-        <v>1325.9</v>
+        <v>1281.5</v>
       </c>
       <c r="H3" t="n">
-        <v>2.73</v>
+        <v>2.3</v>
       </c>
       <c r="I3" t="n">
-        <v>4877325</v>
+        <v>1687323</v>
       </c>
       <c r="J3" t="n">
-        <v>65745.365535</v>
+        <v>22012.4783934</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -2175,22 +2067,22 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>25-Jul-2025</t>
+          <t>01-Aug-2025</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Dividend - Rs 3.60 Per Share</t>
+          <t>Dividend - Rs 8 Per Share</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.73</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>UNITDSPR</t>
+          <t>BOSCHLTD</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -2199,28 +2091,28 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1319</v>
+        <v>39455</v>
       </c>
       <c r="D4" t="n">
-        <v>1332.9</v>
+        <v>40350</v>
       </c>
       <c r="E4" t="n">
-        <v>1299.9</v>
+        <v>39060</v>
       </c>
       <c r="F4" t="n">
-        <v>1329.2</v>
+        <v>39960</v>
       </c>
       <c r="G4" t="n">
-        <v>1306.2</v>
+        <v>39225</v>
       </c>
       <c r="H4" t="n">
-        <v>1.76</v>
+        <v>1.87</v>
       </c>
       <c r="I4" t="n">
-        <v>802593</v>
+        <v>46252</v>
       </c>
       <c r="J4" t="n">
-        <v>10596.635379</v>
+        <v>18422.8838808</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -2229,22 +2121,22 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>01-Aug-2025</t>
+          <t>29-Jul-2025</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Dividend - Rs 8 Per Share</t>
+          <t>Dividend - Rs 512 Per Share</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.76</v>
+        <v>1.87</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>HAVELLS</t>
+          <t>BRITANNIA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2253,28 +2145,28 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1467.4</v>
+        <v>5671</v>
       </c>
       <c r="D5" t="n">
-        <v>1487.9</v>
+        <v>5893.5</v>
       </c>
       <c r="E5" t="n">
-        <v>1463.1</v>
+        <v>5671</v>
       </c>
       <c r="F5" t="n">
-        <v>1485</v>
+        <v>5819</v>
       </c>
       <c r="G5" t="n">
-        <v>1465.9</v>
+        <v>5721</v>
       </c>
       <c r="H5" t="n">
-        <v>1.3</v>
+        <v>1.71</v>
       </c>
       <c r="I5" t="n">
-        <v>589304</v>
+        <v>699161</v>
       </c>
       <c r="J5" t="n">
-        <v>8679.4461032</v>
+        <v>40759.1985653</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -2283,22 +2175,22 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>23-May-2025</t>
+          <t>04-Aug-2025</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Annual General Meeting/Dividend - Rs 6 Per Share</t>
+          <t>Dividend - Rs 75 Per Share</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.3</v>
+        <v>1.71</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ICICIPRULI</t>
+          <t>DABUR</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2307,28 +2199,28 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>620.6</v>
+        <v>515.45</v>
       </c>
       <c r="D6" t="n">
-        <v>630.95</v>
+        <v>528.55</v>
       </c>
       <c r="E6" t="n">
-        <v>619.95</v>
+        <v>509.7</v>
       </c>
       <c r="F6" t="n">
-        <v>629</v>
+        <v>521.55</v>
       </c>
       <c r="G6" t="n">
-        <v>621.3</v>
+        <v>513.85</v>
       </c>
       <c r="H6" t="n">
-        <v>1.24</v>
+        <v>1.5</v>
       </c>
       <c r="I6" t="n">
-        <v>926442</v>
+        <v>3745766</v>
       </c>
       <c r="J6" t="n">
-        <v>5824.8187866</v>
+        <v>19467.8696318</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -2337,22 +2229,22 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>12-Jun-2025</t>
+          <t>18-Jul-2025</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Dividend - Re 0.85 Per Share</t>
+          <t>Dividend - Rs 5.25 Per Share</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.24</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DMART</t>
+          <t>GAIL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2361,28 +2253,28 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>4334.6</v>
+        <v>170.18</v>
       </c>
       <c r="D7" t="n">
-        <v>4394.9</v>
+        <v>174</v>
       </c>
       <c r="E7" t="n">
-        <v>4327.1</v>
+        <v>170.06</v>
       </c>
       <c r="F7" t="n">
-        <v>4376.5</v>
+        <v>173.2</v>
       </c>
       <c r="G7" t="n">
-        <v>4334.6</v>
+        <v>171.22</v>
       </c>
       <c r="H7" t="n">
-        <v>0.97</v>
+        <v>1.16</v>
       </c>
       <c r="I7" t="n">
-        <v>302644</v>
+        <v>8823629</v>
       </c>
       <c r="J7" t="n">
-        <v>13210.1382204</v>
+        <v>15220.760025</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -2391,22 +2283,22 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>09-Aug-2021</t>
+          <t>04-Aug-2025</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Dividend - Re 1 Per Share</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0.97</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>LODHA</t>
+          <t>DMART</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2415,28 +2307,28 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1229.9</v>
+        <v>4720</v>
       </c>
       <c r="D8" t="n">
-        <v>1239.9</v>
+        <v>4800.5</v>
       </c>
       <c r="E8" t="n">
-        <v>1228.5</v>
+        <v>4680</v>
       </c>
       <c r="F8" t="n">
-        <v>1234.8</v>
+        <v>4752</v>
       </c>
       <c r="G8" t="n">
-        <v>1225.8</v>
+        <v>4699.9</v>
       </c>
       <c r="H8" t="n">
-        <v>0.73</v>
+        <v>1.11</v>
       </c>
       <c r="I8" t="n">
-        <v>412837</v>
+        <v>591567</v>
       </c>
       <c r="J8" t="n">
-        <v>5094.8627007</v>
+        <v>28058.2594368</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -2445,22 +2337,22 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>16-Aug-2024</t>
+          <t>09-Aug-2021</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Dividend - Rs 2.25 Per Share</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0.73</v>
+        <v>1.11</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG</t>
+          <t>MOTHERSON</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2469,28 +2361,28 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>13970</v>
+        <v>92.2</v>
       </c>
       <c r="D9" t="n">
-        <v>14079</v>
+        <v>95.06999999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>13900</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>14019</v>
+        <v>92.98999999999999</v>
       </c>
       <c r="G9" t="n">
-        <v>13917</v>
+        <v>92.11</v>
       </c>
       <c r="H9" t="n">
-        <v>0.73</v>
+        <v>0.96</v>
       </c>
       <c r="I9" t="n">
-        <v>6758</v>
+        <v>28080321</v>
       </c>
       <c r="J9" t="n">
-        <v>945.5563828000001</v>
+        <v>26128.7386905</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -2499,22 +2391,22 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>27-Jun-2025</t>
+          <t>18-Jul-2025</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Dividend - Rs 28 Per Share</t>
+          <t>Bonus 1:2</t>
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0.73</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>TORNTPHARM</t>
+          <t>TATAPOWER</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2523,28 +2415,28 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3621.3</v>
+        <v>371.1</v>
       </c>
       <c r="D10" t="n">
-        <v>3647.7</v>
+        <v>375</v>
       </c>
       <c r="E10" t="n">
-        <v>3593.9</v>
+        <v>368.5</v>
       </c>
       <c r="F10" t="n">
-        <v>3641.3</v>
+        <v>374.45</v>
       </c>
       <c r="G10" t="n">
-        <v>3617.8</v>
+        <v>371.1</v>
       </c>
       <c r="H10" t="n">
-        <v>0.65</v>
+        <v>0.9</v>
       </c>
       <c r="I10" t="n">
-        <v>194609</v>
+        <v>5793121</v>
       </c>
       <c r="J10" t="n">
-        <v>7064.7543007</v>
+        <v>21642.5207439</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -2558,17 +2450,17 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Dividend - Rs 6 Per Share</t>
+          <t>Dividend - Rs 2.25 Per Share</t>
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0.65</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>LICI</t>
+          <t>TVSMOTOR</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2577,28 +2469,28 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>890</v>
+        <v>3239.1</v>
       </c>
       <c r="D11" t="n">
-        <v>894.3</v>
+        <v>3313.9</v>
       </c>
       <c r="E11" t="n">
-        <v>885</v>
+        <v>3238</v>
       </c>
       <c r="F11" t="n">
-        <v>892.75</v>
+        <v>3285</v>
       </c>
       <c r="G11" t="n">
-        <v>887.5</v>
+        <v>3256</v>
       </c>
       <c r="H11" t="n">
-        <v>0.59</v>
+        <v>0.89</v>
       </c>
       <c r="I11" t="n">
-        <v>412698</v>
+        <v>1023381</v>
       </c>
       <c r="J11" t="n">
-        <v>3669.5868066</v>
+        <v>33691.4422677</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -2607,22 +2499,22 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>25-Jul-2025</t>
+          <t>25-Aug-2025</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Dividend - Rs 12 Per Share</t>
+          <t>Scheme Of Arrangement - Bonus Ncrps 4:1</t>
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0.59</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>LTIM</t>
+          <t>ADANIPOWER</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2631,28 +2523,28 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>5150</v>
+        <v>598.4</v>
       </c>
       <c r="D12" t="n">
-        <v>5272</v>
+        <v>603.2</v>
       </c>
       <c r="E12" t="n">
-        <v>5127.5</v>
+        <v>583.5</v>
       </c>
       <c r="F12" t="n">
-        <v>5139</v>
+        <v>599.75</v>
       </c>
       <c r="G12" t="n">
-        <v>5114.5</v>
+        <v>594.95</v>
       </c>
       <c r="H12" t="n">
-        <v>0.48</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>270892</v>
+        <v>3619098</v>
       </c>
       <c r="J12" t="n">
-        <v>14091.9914644</v>
+        <v>21481.156179</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -2661,22 +2553,22 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>23-May-2025</t>
+          <t>14-Jun-2024</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Dividend - Rs 45 Per Share</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
       <c r="N12" t="n">
-        <v>0.48</v>
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>INDIGO</t>
+          <t>HYUNDAI</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2685,28 +2577,28 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>5978</v>
+        <v>2452.6</v>
       </c>
       <c r="D13" t="n">
-        <v>6055</v>
+        <v>2494</v>
       </c>
       <c r="E13" t="n">
-        <v>5955.5</v>
+        <v>2438.8</v>
       </c>
       <c r="F13" t="n">
-        <v>5996</v>
+        <v>2456.1</v>
       </c>
       <c r="G13" t="n">
-        <v>5969.5</v>
+        <v>2441.4</v>
       </c>
       <c r="H13" t="n">
-        <v>0.44</v>
+        <v>0.6</v>
       </c>
       <c r="I13" t="n">
-        <v>344908</v>
+        <v>595068</v>
       </c>
       <c r="J13" t="n">
-        <v>20732.0404812</v>
+        <v>14633.614722</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -2715,22 +2607,22 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>13-Aug-2025</t>
+          <t>05-Aug-2025</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Dividend - Rs 10 Per Share</t>
+          <t>Dividend - Rs 21 Per Share</t>
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0.44</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>GAIL</t>
+          <t>SIEMENS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2739,28 +2631,28 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>173.06</v>
+        <v>3043.1</v>
       </c>
       <c r="D14" t="n">
-        <v>174.8</v>
+        <v>3094</v>
       </c>
       <c r="E14" t="n">
-        <v>172.87</v>
+        <v>3017.5</v>
       </c>
       <c r="F14" t="n">
-        <v>174.12</v>
+        <v>3061.2</v>
       </c>
       <c r="G14" t="n">
-        <v>173.36</v>
+        <v>3043.2</v>
       </c>
       <c r="H14" t="n">
-        <v>0.44</v>
+        <v>0.59</v>
       </c>
       <c r="I14" t="n">
-        <v>2545491</v>
+        <v>430652</v>
       </c>
       <c r="J14" t="n">
-        <v>4422.2815143</v>
+        <v>13184.7985668</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -2769,22 +2661,22 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>04-Aug-2025</t>
+          <t>07-Apr-2025</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Dividend - Re 1 Per Share</t>
+          <t>Demerger</t>
         </is>
       </c>
       <c r="N14" t="n">
-        <v>0.44</v>
+        <v>0.59</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CANBK</t>
+          <t>ZYDUSLIFE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2793,28 +2685,28 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>109.5</v>
+        <v>984.3</v>
       </c>
       <c r="D15" t="n">
-        <v>109.88</v>
+        <v>988.5</v>
       </c>
       <c r="E15" t="n">
-        <v>108.63</v>
+        <v>969.2</v>
       </c>
       <c r="F15" t="n">
-        <v>109.3</v>
+        <v>983</v>
       </c>
       <c r="G15" t="n">
-        <v>108.99</v>
+        <v>978.6</v>
       </c>
       <c r="H15" t="n">
-        <v>0.28</v>
+        <v>0.45</v>
       </c>
       <c r="I15" t="n">
-        <v>6237855</v>
+        <v>833114</v>
       </c>
       <c r="J15" t="n">
-        <v>6814.8565875</v>
+        <v>8162.9342834</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -2823,22 +2715,22 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>13-Jun-2025</t>
+          <t>25-Jul-2025</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Dividend - Rs 4 Per Share</t>
+          <t>Dividend - Rs 11 Per Share</t>
         </is>
       </c>
       <c r="N15" t="n">
-        <v>0.28</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>DIVISLAB</t>
+          <t>HAVELLS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2847,28 +2739,28 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>6155</v>
+        <v>1512</v>
       </c>
       <c r="D16" t="n">
-        <v>6205</v>
+        <v>1538.3</v>
       </c>
       <c r="E16" t="n">
-        <v>6100</v>
+        <v>1512</v>
       </c>
       <c r="F16" t="n">
-        <v>6117</v>
+        <v>1525.5</v>
       </c>
       <c r="G16" t="n">
-        <v>6100.5</v>
+        <v>1519.4</v>
       </c>
       <c r="H16" t="n">
-        <v>0.27</v>
+        <v>0.4</v>
       </c>
       <c r="I16" t="n">
-        <v>173576</v>
+        <v>1112664</v>
       </c>
       <c r="J16" t="n">
-        <v>10679.7667704</v>
+        <v>17000.949588</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -2877,22 +2769,22 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>25-Jul-2025</t>
+          <t>23-May-2025</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Dividend - Rs 30 Per Share</t>
+          <t>Annual General Meeting/Dividend - Rs 6 Per Share</t>
         </is>
       </c>
       <c r="N16" t="n">
-        <v>0.27</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>BANKBARODA</t>
+          <t>AMBUJACEM</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2901,28 +2793,28 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>241.99</v>
+        <v>563</v>
       </c>
       <c r="D17" t="n">
-        <v>243.8</v>
+        <v>569.2</v>
       </c>
       <c r="E17" t="n">
-        <v>241.4</v>
+        <v>560</v>
       </c>
       <c r="F17" t="n">
-        <v>242.46</v>
+        <v>563.2</v>
       </c>
       <c r="G17" t="n">
-        <v>241.81</v>
+        <v>561.8</v>
       </c>
       <c r="H17" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="I17" t="n">
-        <v>2083270</v>
+        <v>1166207</v>
       </c>
       <c r="J17" t="n">
-        <v>5049.638153</v>
+        <v>6586.5038946</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -2931,232 +2823,16 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>06-Jun-2025</t>
+          <t>13-Jun-2025</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Dividend - Rs 8.35 Per Share</t>
+          <t>Dividend - Rs 2 Per Share</t>
         </is>
       </c>
       <c r="N17" t="n">
-        <v>0.27</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>TVSMOTOR</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>EQ</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>3034</v>
-      </c>
-      <c r="D18" t="n">
-        <v>3039.9</v>
-      </c>
-      <c r="E18" t="n">
-        <v>2985.6</v>
-      </c>
-      <c r="F18" t="n">
-        <v>3027</v>
-      </c>
-      <c r="G18" t="n">
-        <v>3019.2</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="I18" t="n">
-        <v>382634</v>
-      </c>
-      <c r="J18" t="n">
-        <v>11502.4372008</v>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>26-Mar-2025</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>Interim Dividend - Rs 10 Per Share</t>
-        </is>
-      </c>
-      <c r="N18" t="n">
-        <v>0.26</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>SIEMENS</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>EQ</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>3150.7</v>
-      </c>
-      <c r="D19" t="n">
-        <v>3166.9</v>
-      </c>
-      <c r="E19" t="n">
-        <v>3118.2</v>
-      </c>
-      <c r="F19" t="n">
-        <v>3157</v>
-      </c>
-      <c r="G19" t="n">
-        <v>3150.7</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="I19" t="n">
-        <v>128862</v>
-      </c>
-      <c r="J19" t="n">
-        <v>4055.7510432</v>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>07-Apr-2025</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>Demerger</t>
-        </is>
-      </c>
-      <c r="N19" t="n">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>CHOLAFIN</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>EQ</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>1459.1</v>
-      </c>
-      <c r="D20" t="n">
-        <v>1474.8</v>
-      </c>
-      <c r="E20" t="n">
-        <v>1459.1</v>
-      </c>
-      <c r="F20" t="n">
-        <v>1463.3</v>
-      </c>
-      <c r="G20" t="n">
-        <v>1460.5</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="I20" t="n">
-        <v>266753</v>
-      </c>
-      <c r="J20" t="n">
-        <v>3916.5742472</v>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>24-Jul-2025</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>Dividend - Re 0.70 Per Share</t>
-        </is>
-      </c>
-      <c r="N20" t="n">
-        <v>0.19</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>PIDILITIND</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>EQ</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>3061.1</v>
-      </c>
-      <c r="D21" t="n">
-        <v>3075</v>
-      </c>
-      <c r="E21" t="n">
-        <v>3055.1</v>
-      </c>
-      <c r="F21" t="n">
-        <v>3067.3</v>
-      </c>
-      <c r="G21" t="n">
-        <v>3061.9</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="I21" t="n">
-        <v>55581</v>
-      </c>
-      <c r="J21" t="n">
-        <v>1704.6581538</v>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>13-Aug-2025</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>Special Dividend - Rs 10 Per Share</t>
-        </is>
-      </c>
-      <c r="N21" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
     </row>
   </sheetData>
@@ -3248,7 +2924,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MUTHOOTFIN</t>
+          <t>SAMMAANCAP</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -3257,28 +2933,28 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2730</v>
+        <v>119.3</v>
       </c>
       <c r="D2" t="n">
-        <v>2800</v>
+        <v>126.83</v>
       </c>
       <c r="E2" t="n">
-        <v>2671.3</v>
+        <v>118.55</v>
       </c>
       <c r="F2" t="n">
-        <v>2774.5</v>
+        <v>124.2</v>
       </c>
       <c r="G2" t="n">
-        <v>2509.9</v>
+        <v>117.97</v>
       </c>
       <c r="H2" t="n">
-        <v>10.54</v>
+        <v>5.28</v>
       </c>
       <c r="I2" t="n">
-        <v>6922821</v>
+        <v>68804305</v>
       </c>
       <c r="J2" t="n">
-        <v>191255.3912028</v>
+        <v>85482.468532</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -3287,22 +2963,22 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>25-Apr-2025</t>
+          <t>20-Sep-2024</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Interim Dividend - Rs 26 Per Share</t>
+          <t>Dividend - Rs 2 Per Share</t>
         </is>
       </c>
       <c r="N2" t="n">
-        <v>10.54</v>
+        <v>5.28</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>NAUKRI</t>
+          <t>CGPOWER</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -3311,28 +2987,28 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1329</v>
+        <v>676.95</v>
       </c>
       <c r="D3" t="n">
-        <v>1374.5</v>
+        <v>699.75</v>
       </c>
       <c r="E3" t="n">
-        <v>1319.5</v>
+        <v>668.25</v>
       </c>
       <c r="F3" t="n">
-        <v>1362.1</v>
+        <v>694</v>
       </c>
       <c r="G3" t="n">
-        <v>1325.9</v>
+        <v>664</v>
       </c>
       <c r="H3" t="n">
-        <v>2.73</v>
+        <v>4.52</v>
       </c>
       <c r="I3" t="n">
-        <v>4877325</v>
+        <v>14580868</v>
       </c>
       <c r="J3" t="n">
-        <v>65745.365535</v>
+        <v>100278.4615832</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -3341,22 +3017,22 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>25-Jul-2025</t>
+          <t>21-Mar-2025</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Dividend - Rs 3.60 Per Share</t>
+          <t>Interim Dividend - Rs 1.30 Per Share</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.73</v>
+        <v>4.52</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>MANAPPURAM</t>
+          <t>RBLBANK</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -3365,28 +3041,28 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>260</v>
+        <v>251.5</v>
       </c>
       <c r="D4" t="n">
-        <v>266.5</v>
+        <v>267.35</v>
       </c>
       <c r="E4" t="n">
-        <v>258.7</v>
+        <v>251.5</v>
       </c>
       <c r="F4" t="n">
-        <v>261.65</v>
+        <v>262</v>
       </c>
       <c r="G4" t="n">
-        <v>255.9</v>
+        <v>250.85</v>
       </c>
       <c r="H4" t="n">
-        <v>2.45</v>
+        <v>4.44</v>
       </c>
       <c r="I4" t="n">
-        <v>10704967</v>
+        <v>65899998</v>
       </c>
       <c r="J4" t="n">
-        <v>28155.1337067</v>
+        <v>172018.7647794</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -3395,22 +3071,22 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>14-Aug-2025</t>
+          <t>26-Jul-2024</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Interim Dividend - Rs 0.50 Per Share</t>
+          <t>Dividend - Rs 1.50 Per Share</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.25</v>
+        <v>4.44</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>WIPRO</t>
+          <t>COLPAL</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -3419,28 +3095,28 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>243.1</v>
+        <v>2250</v>
       </c>
       <c r="D5" t="n">
-        <v>248.43</v>
+        <v>2357.9</v>
       </c>
       <c r="E5" t="n">
-        <v>242.41</v>
+        <v>2250</v>
       </c>
       <c r="F5" t="n">
-        <v>247.1</v>
+        <v>2328.6</v>
       </c>
       <c r="G5" t="n">
-        <v>241.65</v>
+        <v>2262.7</v>
       </c>
       <c r="H5" t="n">
-        <v>2.26</v>
+        <v>2.91</v>
       </c>
       <c r="I5" t="n">
-        <v>6604129</v>
+        <v>1598897</v>
       </c>
       <c r="J5" t="n">
-        <v>16255.4031206</v>
+        <v>37283.080246</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -3449,22 +3125,22 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>28-Jul-2025</t>
+          <t>28-May-2025</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Interim Dividend - Rs 5 Per Share</t>
+          <t>Interim Dividend - Rs 27 Per Share</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.26</v>
+        <v>2.91</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>INFY</t>
+          <t>YESBANK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -3473,28 +3149,28 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1426.2</v>
+        <v>18.88</v>
       </c>
       <c r="D6" t="n">
-        <v>1470</v>
+        <v>19.55</v>
       </c>
       <c r="E6" t="n">
-        <v>1426.2</v>
+        <v>18.71</v>
       </c>
       <c r="F6" t="n">
-        <v>1455.4</v>
+        <v>19.14</v>
       </c>
       <c r="G6" t="n">
-        <v>1426.6</v>
+        <v>18.68</v>
       </c>
       <c r="H6" t="n">
-        <v>2.02</v>
+        <v>2.46</v>
       </c>
       <c r="I6" t="n">
-        <v>7582525</v>
+        <v>191492999</v>
       </c>
       <c r="J6" t="n">
-        <v>110182.4290275</v>
+        <v>36747.5065081</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -3503,22 +3179,22 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>30-May-2025</t>
+          <t>03-Jun-2019</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Dividend - Rs 22 Per Share</t>
+          <t>Annual General Meeting/ Dividend - Rs 2 Per Share</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.02</v>
+        <v>2.46</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>UNOMINDA</t>
+          <t>UNITDSPR</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3527,28 +3203,28 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1114.5</v>
+        <v>1290</v>
       </c>
       <c r="D7" t="n">
-        <v>1140.9</v>
+        <v>1315.3</v>
       </c>
       <c r="E7" t="n">
-        <v>1114.4</v>
+        <v>1284.2</v>
       </c>
       <c r="F7" t="n">
-        <v>1136.1</v>
+        <v>1311</v>
       </c>
       <c r="G7" t="n">
-        <v>1114.4</v>
+        <v>1281.5</v>
       </c>
       <c r="H7" t="n">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="I7" t="n">
-        <v>803722</v>
+        <v>1687323</v>
       </c>
       <c r="J7" t="n">
-        <v>9110.5103588</v>
+        <v>22012.4783934</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -3557,22 +3233,22 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>30-May-2025</t>
+          <t>01-Aug-2025</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Dividend - Rs 1.50 Per Share</t>
+          <t>Dividend - Rs 8 Per Share</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>GMRAIRPORT</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3581,28 +3257,28 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>88.73999999999999</v>
+        <v>402</v>
       </c>
       <c r="D8" t="n">
-        <v>90.55</v>
+        <v>410.45</v>
       </c>
       <c r="E8" t="n">
-        <v>88.73999999999999</v>
+        <v>401.9</v>
       </c>
       <c r="F8" t="n">
-        <v>90.27</v>
+        <v>409.5</v>
       </c>
       <c r="G8" t="n">
-        <v>88.65000000000001</v>
+        <v>400.9</v>
       </c>
       <c r="H8" t="n">
-        <v>1.83</v>
+        <v>2.15</v>
       </c>
       <c r="I8" t="n">
-        <v>2588178</v>
+        <v>25255050</v>
       </c>
       <c r="J8" t="n">
-        <v>2331.1719246</v>
+        <v>102924.43077</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -3611,22 +3287,22 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>05-Sep-2024</t>
+          <t>28-May-2025</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Dividend - Rs 7.85 Per Share</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.83</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>KALYANKJIL</t>
+          <t>MARICO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3635,28 +3311,28 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>517</v>
+        <v>710</v>
       </c>
       <c r="D9" t="n">
-        <v>532.7</v>
+        <v>727</v>
       </c>
       <c r="E9" t="n">
-        <v>511.45</v>
+        <v>709.3</v>
       </c>
       <c r="F9" t="n">
-        <v>524.85</v>
+        <v>726</v>
       </c>
       <c r="G9" t="n">
-        <v>515.65</v>
+        <v>711.6</v>
       </c>
       <c r="H9" t="n">
-        <v>1.78</v>
+        <v>2.02</v>
       </c>
       <c r="I9" t="n">
-        <v>4671246</v>
+        <v>2136019</v>
       </c>
       <c r="J9" t="n">
-        <v>24473.5920432</v>
+        <v>15432.5236731</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -3665,22 +3341,22 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>09-Aug-2024</t>
+          <t>01-Aug-2025</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Annual General Meeting/Dividend - Rs 1.20 Per Share</t>
+          <t>Dividend - Rs 7 Per Share</t>
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.78</v>
+        <v>2.02</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>UNITDSPR</t>
+          <t>DALBHARAT</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -3689,28 +3365,28 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1319</v>
+        <v>2365</v>
       </c>
       <c r="D10" t="n">
-        <v>1332.9</v>
+        <v>2408.5</v>
       </c>
       <c r="E10" t="n">
-        <v>1299.9</v>
+        <v>2355</v>
       </c>
       <c r="F10" t="n">
-        <v>1329.2</v>
+        <v>2395.9</v>
       </c>
       <c r="G10" t="n">
-        <v>1306.2</v>
+        <v>2351.4</v>
       </c>
       <c r="H10" t="n">
-        <v>1.76</v>
+        <v>1.89</v>
       </c>
       <c r="I10" t="n">
-        <v>802593</v>
+        <v>423429</v>
       </c>
       <c r="J10" t="n">
-        <v>10596.635379</v>
+        <v>10146.9255273</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -3719,22 +3395,22 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>01-Aug-2025</t>
+          <t>23-Jun-2025</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Dividend - Rs 8 Per Share</t>
+          <t>Annual General Meeting/Dividend - Rs 5 Per Share</t>
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.76</v>
+        <v>1.89</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AUBANK</t>
+          <t>BOSCHLTD</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3743,28 +3419,28 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>744</v>
+        <v>39455</v>
       </c>
       <c r="D11" t="n">
-        <v>751.8</v>
+        <v>40350</v>
       </c>
       <c r="E11" t="n">
-        <v>740.55</v>
+        <v>39060</v>
       </c>
       <c r="F11" t="n">
-        <v>750.8</v>
+        <v>39960</v>
       </c>
       <c r="G11" t="n">
-        <v>738</v>
+        <v>39225</v>
       </c>
       <c r="H11" t="n">
-        <v>1.73</v>
+        <v>1.87</v>
       </c>
       <c r="I11" t="n">
-        <v>917891</v>
+        <v>46252</v>
       </c>
       <c r="J11" t="n">
-        <v>6865.273945399999</v>
+        <v>18422.8838808</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -3773,22 +3449,22 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>04-Jul-2025</t>
+          <t>29-Jul-2025</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Dividend - Re 1 Per Share</t>
+          <t>Dividend - Rs 512 Per Share</t>
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.73</v>
+        <v>1.87</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ABFRL</t>
+          <t>CROMPTON</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3797,28 +3473,28 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>74.5</v>
+        <v>323.05</v>
       </c>
       <c r="D12" t="n">
-        <v>76.58</v>
+        <v>334.4</v>
       </c>
       <c r="E12" t="n">
-        <v>74.20999999999999</v>
+        <v>323.05</v>
       </c>
       <c r="F12" t="n">
-        <v>75.8</v>
+        <v>330.05</v>
       </c>
       <c r="G12" t="n">
-        <v>74.68000000000001</v>
+        <v>324.05</v>
       </c>
       <c r="H12" t="n">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="I12" t="n">
-        <v>5227661</v>
+        <v>3392084</v>
       </c>
       <c r="J12" t="n">
-        <v>3962.567038</v>
+        <v>11206.7671192</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -3827,22 +3503,22 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>22-May-2025</t>
+          <t>24-Jul-2025</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Demerger</t>
+          <t>Dividend - Rs 3 Per Share</t>
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>HDFCLIFE</t>
+          <t>SHRIRAMFIN</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3851,28 +3527,28 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>778.75</v>
+        <v>570.5</v>
       </c>
       <c r="D13" t="n">
-        <v>790.75</v>
+        <v>588.65</v>
       </c>
       <c r="E13" t="n">
-        <v>777.95</v>
+        <v>566.5</v>
       </c>
       <c r="F13" t="n">
-        <v>787.05</v>
+        <v>581.9</v>
       </c>
       <c r="G13" t="n">
-        <v>776.6</v>
+        <v>571.65</v>
       </c>
       <c r="H13" t="n">
-        <v>1.35</v>
+        <v>1.79</v>
       </c>
       <c r="I13" t="n">
-        <v>1551742</v>
+        <v>12979613</v>
       </c>
       <c r="J13" t="n">
-        <v>12215.313024</v>
+        <v>71144.685432</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -3881,22 +3557,22 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>20-Jun-2025</t>
+          <t>11-Jul-2025</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Dividend - Rs 2.10 Per Share</t>
+          <t>Dividend - Rs 3 Per Share</t>
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.35</v>
+        <v>1.79</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>HAVELLS</t>
+          <t>BRITANNIA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3905,28 +3581,28 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1467.4</v>
+        <v>5671</v>
       </c>
       <c r="D14" t="n">
-        <v>1487.9</v>
+        <v>5893.5</v>
       </c>
       <c r="E14" t="n">
-        <v>1463.1</v>
+        <v>5671</v>
       </c>
       <c r="F14" t="n">
-        <v>1485</v>
+        <v>5819</v>
       </c>
       <c r="G14" t="n">
-        <v>1465.9</v>
+        <v>5721</v>
       </c>
       <c r="H14" t="n">
-        <v>1.3</v>
+        <v>1.71</v>
       </c>
       <c r="I14" t="n">
-        <v>589304</v>
+        <v>699161</v>
       </c>
       <c r="J14" t="n">
-        <v>8679.4461032</v>
+        <v>40759.1985653</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -3935,22 +3611,22 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>23-May-2025</t>
+          <t>04-Aug-2025</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Annual General Meeting/Dividend - Rs 6 Per Share</t>
+          <t>Dividend - Rs 75 Per Share</t>
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.3</v>
+        <v>1.71</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ICICIPRULI</t>
+          <t>BEL</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3959,28 +3635,28 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>620.6</v>
+        <v>362.3</v>
       </c>
       <c r="D15" t="n">
-        <v>630.95</v>
+        <v>371</v>
       </c>
       <c r="E15" t="n">
-        <v>619.95</v>
+        <v>361.6</v>
       </c>
       <c r="F15" t="n">
-        <v>629</v>
+        <v>369.4</v>
       </c>
       <c r="G15" t="n">
-        <v>621.3</v>
+        <v>363.85</v>
       </c>
       <c r="H15" t="n">
-        <v>1.24</v>
+        <v>1.53</v>
       </c>
       <c r="I15" t="n">
-        <v>926442</v>
+        <v>12739664</v>
       </c>
       <c r="J15" t="n">
-        <v>5824.8187866</v>
+        <v>46938.0180416</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -3989,22 +3665,22 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>12-Jun-2025</t>
+          <t>14-Aug-2025</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Dividend - Re 0.85 Per Share</t>
+          <t>Dividend - Rs 0.90 Per Share</t>
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.24</v>
+        <v>1.53</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>PGEL</t>
+          <t>INDUSTOWER</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -4013,28 +3689,28 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>488</v>
+        <v>337</v>
       </c>
       <c r="D16" t="n">
-        <v>495.5</v>
+        <v>346.45</v>
       </c>
       <c r="E16" t="n">
-        <v>465</v>
+        <v>336</v>
       </c>
       <c r="F16" t="n">
-        <v>492.1</v>
+        <v>340.7</v>
       </c>
       <c r="G16" t="n">
-        <v>486.1</v>
+        <v>335.6</v>
       </c>
       <c r="H16" t="n">
-        <v>1.23</v>
+        <v>1.52</v>
       </c>
       <c r="I16" t="n">
-        <v>2878384</v>
+        <v>7338329</v>
       </c>
       <c r="J16" t="n">
-        <v>13993.8394928</v>
+        <v>25029.5725532</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -4043,22 +3719,22 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>23-Sep-2024</t>
+          <t>09-Aug-2024</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Dividend - Rs 0.20 Per Share</t>
+          <t>Buy Back</t>
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.23</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>DABUR</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -4067,28 +3743,28 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>313</v>
+        <v>515.45</v>
       </c>
       <c r="D17" t="n">
-        <v>316.55</v>
+        <v>528.55</v>
       </c>
       <c r="E17" t="n">
-        <v>310.65</v>
+        <v>509.7</v>
       </c>
       <c r="F17" t="n">
-        <v>316</v>
+        <v>521.55</v>
       </c>
       <c r="G17" t="n">
-        <v>312.35</v>
+        <v>513.85</v>
       </c>
       <c r="H17" t="n">
-        <v>1.17</v>
+        <v>1.5</v>
       </c>
       <c r="I17" t="n">
-        <v>17571060</v>
+        <v>3745766</v>
       </c>
       <c r="J17" t="n">
-        <v>55069.459146</v>
+        <v>19467.8696318</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -4097,22 +3773,22 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>18-Jul-2025</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Dividend - Rs 5.25 Per Share</t>
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.17</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>KAYNES</t>
+          <t>LICHSGFIN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -4121,28 +3797,28 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>6095</v>
+        <v>545.4</v>
       </c>
       <c r="D18" t="n">
-        <v>6174.5</v>
+        <v>558.35</v>
       </c>
       <c r="E18" t="n">
-        <v>6031</v>
+        <v>545</v>
       </c>
       <c r="F18" t="n">
-        <v>6128.5</v>
+        <v>555</v>
       </c>
       <c r="G18" t="n">
-        <v>6060</v>
+        <v>547.35</v>
       </c>
       <c r="H18" t="n">
-        <v>1.13</v>
+        <v>1.4</v>
       </c>
       <c r="I18" t="n">
-        <v>215569</v>
+        <v>1722586</v>
       </c>
       <c r="J18" t="n">
-        <v>13197.1126231</v>
+        <v>9530.207044999999</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -4151,22 +3827,22 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>08-Sep-2023</t>
+          <t>22-Aug-2025</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Dividend - Rs 10 Per Share</t>
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.13</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CROMPTON</t>
+          <t>CAMS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4175,28 +3851,28 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>320</v>
+        <v>3654.9</v>
       </c>
       <c r="D19" t="n">
-        <v>324.25</v>
+        <v>3758.9</v>
       </c>
       <c r="E19" t="n">
-        <v>319.45</v>
+        <v>3645</v>
       </c>
       <c r="F19" t="n">
-        <v>322.1</v>
+        <v>3707</v>
       </c>
       <c r="G19" t="n">
-        <v>318.5</v>
+        <v>3657.7</v>
       </c>
       <c r="H19" t="n">
-        <v>1.13</v>
+        <v>1.35</v>
       </c>
       <c r="I19" t="n">
-        <v>628588</v>
+        <v>334539</v>
       </c>
       <c r="J19" t="n">
-        <v>2026.7562884</v>
+        <v>12462.3471897</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -4205,22 +3881,22 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>24-Jul-2025</t>
+          <t>08-Aug-2025</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Dividend - Rs 3 Per Share</t>
+          <t>Interim Dividend - Rs 11 Per Share</t>
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.13</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>360ONE</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4229,28 +3905,28 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1028.1</v>
+        <v>3575.6</v>
       </c>
       <c r="D20" t="n">
-        <v>1044.2</v>
+        <v>3615</v>
       </c>
       <c r="E20" t="n">
-        <v>1022.6</v>
+        <v>3540.2</v>
       </c>
       <c r="F20" t="n">
-        <v>1039.1</v>
+        <v>3605</v>
       </c>
       <c r="G20" t="n">
-        <v>1028</v>
+        <v>3560.1</v>
       </c>
       <c r="H20" t="n">
-        <v>1.08</v>
+        <v>1.26</v>
       </c>
       <c r="I20" t="n">
-        <v>285103</v>
+        <v>1678055</v>
       </c>
       <c r="J20" t="n">
-        <v>2954.8360023</v>
+        <v>60304.262535</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -4259,22 +3935,22 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>29-Apr-2025</t>
+          <t>03-Jun-2025</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Interim Dividend - Rs 6 Per Share</t>
+          <t>Dividend - Rs 34 Per Share</t>
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.08</v>
+        <v>1.26</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
+          <t>ASIANPAINT</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4283,28 +3959,28 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>5265</v>
+        <v>2491</v>
       </c>
       <c r="D21" t="n">
-        <v>5330</v>
+        <v>2531.6</v>
       </c>
       <c r="E21" t="n">
-        <v>5247.5</v>
+        <v>2490</v>
       </c>
       <c r="F21" t="n">
-        <v>5303</v>
+        <v>2520</v>
       </c>
       <c r="G21" t="n">
-        <v>5247.5</v>
+        <v>2489</v>
       </c>
       <c r="H21" t="n">
-        <v>1.06</v>
+        <v>1.25</v>
       </c>
       <c r="I21" t="n">
-        <v>241007</v>
+        <v>1798653</v>
       </c>
       <c r="J21" t="n">
-        <v>12769.1051761</v>
+        <v>45203.9270613</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -4313,16 +3989,16 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>14-Jul-2025</t>
+          <t>10-Jun-2025</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Annual General Meeting/Dividend - Rs 15 Per Share</t>
+          <t>Dividend - Rs 20.55 Per Share</t>
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.06</v>
+        <v>1.25</v>
       </c>
     </row>
   </sheetData>
